--- a/Projects/Nestle Comparamble Valuation/Comparable Company Valuation - Nestle.xlsx
+++ b/Projects/Nestle Comparamble Valuation/Comparable Company Valuation - Nestle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4811e80fe84d3960/Desktop/Finance/Nestle Comp Valuation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4811e80fe84d3960/Desktop/Finance-Portfolio/Projects/Nestle Comparamble Valuation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1366" documentId="11_F25DC773A252ABDACC1048A1491F4F865ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D14152B-6BBA-49FB-85F2-4A564D8EDD52}"/>
+  <xr:revisionPtr revIDLastSave="1411" documentId="11_F25DC773A252ABDACC1048A1491F4F865ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CCCE06A-9C1F-4BFA-833E-B08DAD59D801}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,13 @@
     <sheet name="Appendix" sheetId="5" r:id="rId5"/>
     <sheet name="Rough" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">Appendix!$B$2:$F$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Cover!$B$2:$S$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Inputs!$B$2:$F$25,Inputs!$H$2:$L$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Precedent Transactions'!$B$2:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Trading Comps'!$B$2:$L$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -354,18 +361,18 @@
   <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0&quot;A&quot;"/>
     <numFmt numFmtId="165" formatCode="_(#,##0_)_%;\(#,##0\)_%;_(&quot;–&quot;_)_%;_(@_)_%"/>
-    <numFmt numFmtId="167" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="@\⁽\³\⁾"/>
-    <numFmt numFmtId="169" formatCode="#,##0_);\(#,##0\);\-"/>
-    <numFmt numFmtId="170" formatCode="_(0.0\x_);\(0.0\x\);_(&quot;–&quot;_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
-    <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0"/>
-    <numFmt numFmtId="173" formatCode="0&quot;F&quot;"/>
-    <numFmt numFmtId="174" formatCode="0.0000"/>
-    <numFmt numFmtId="175" formatCode="0.0%"/>
-    <numFmt numFmtId="176" formatCode="dd\/mm\/yyyy"/>
-    <numFmt numFmtId="177" formatCode="#,##0.0;\-#,##0.0"/>
-    <numFmt numFmtId="178" formatCode="mmmm\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="@\⁽\³\⁾"/>
+    <numFmt numFmtId="168" formatCode="#,##0_);\(#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="_(0.0\x_);\(0.0\x\);_(&quot;–&quot;_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="172" formatCode="0&quot;F&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="0.0%"/>
+    <numFmt numFmtId="175" formatCode="dd\/mm\/yyyy"/>
+    <numFmt numFmtId="176" formatCode="#,##0.0;\-#,##0.0"/>
+    <numFmt numFmtId="177" formatCode="mmmm\,\ yyyy"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -1090,7 +1097,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1101,10 +1108,10 @@
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1120,7 +1127,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1129,8 +1136,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1145,8 +1152,8 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1169,10 +1176,10 @@
     <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1187,13 +1194,13 @@
     <xf numFmtId="37" fontId="26" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="26" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1202,37 +1209,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="30" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="30" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1241,18 +1233,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1262,35 +1242,11 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1310,10 +1266,10 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1322,20 +1278,20 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1344,12 +1300,6 @@
     <xf numFmtId="37" fontId="8" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1362,7 +1312,7 @@
     <xf numFmtId="164" fontId="24" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="24" fillId="5" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="24" fillId="5" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1371,10 +1321,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="24" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="24" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="4" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="27" fillId="4" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1386,104 +1336,98 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="8" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="8" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="3" fillId="7" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="3" fillId="7" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="7" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="7" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1492,25 +1436,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1519,25 +1463,22 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="8" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="8" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1545,11 +1486,62 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1570,10 +1562,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1839,713 +1827,726 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:T33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="55" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="55" customWidth="1"/>
-    <col min="3" max="13" width="9.140625" style="55"/>
-    <col min="14" max="14" width="12" style="55" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.28515625" style="55" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" style="55" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="55"/>
-    <col min="18" max="18" width="10.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="55"/>
+    <col min="1" max="1" width="4.7109375" style="51" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="51" customWidth="1"/>
+    <col min="3" max="13" width="9.140625" style="51"/>
+    <col min="14" max="14" width="12" style="51" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" style="51" customWidth="1"/>
+    <col min="16" max="16" width="10.42578125" style="51" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="51"/>
+    <col min="18" max="18" width="10.140625" style="51" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="51"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:20">
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
     </row>
     <row r="3" spans="2:20" ht="15" customHeight="1">
-      <c r="B3" s="54"/>
-      <c r="C3" s="56" t="s">
+      <c r="B3" s="50"/>
+      <c r="C3" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="158"/>
+      <c r="O3" s="158"/>
       <c r="P3" s="27"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
     </row>
     <row r="4" spans="2:20" ht="15" customHeight="1">
-      <c r="B4" s="54"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="158"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="158"/>
+      <c r="L4" s="158"/>
+      <c r="M4" s="158"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="158"/>
       <c r="P4" s="27"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
     </row>
     <row r="5" spans="2:20" ht="15" customHeight="1">
-      <c r="B5" s="54"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
+      <c r="L5" s="158"/>
+      <c r="M5" s="158"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
       <c r="P5" s="27"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="59"/>
-      <c r="S5" s="59"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
     </row>
     <row r="6" spans="2:20" ht="15" customHeight="1">
-      <c r="B6" s="54"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
+      <c r="F6" s="158"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="158"/>
+      <c r="K6" s="158"/>
+      <c r="L6" s="158"/>
+      <c r="M6" s="158"/>
+      <c r="N6" s="158"/>
+      <c r="O6" s="158"/>
       <c r="P6" s="27"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
     </row>
     <row r="7" spans="2:20" ht="15" customHeight="1">
-      <c r="B7" s="54"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="158"/>
+      <c r="M7" s="158"/>
+      <c r="N7" s="158"/>
+      <c r="O7" s="158"/>
       <c r="P7" s="27"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="53"/>
     </row>
     <row r="8" spans="2:20" ht="35.25">
-      <c r="B8" s="54"/>
-      <c r="C8" s="60" t="s">
+      <c r="B8" s="50"/>
+      <c r="C8" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
     </row>
     <row r="9" spans="2:20">
-      <c r="B9" s="54"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="58"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="58"/>
     </row>
     <row r="11" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B11" s="63"/>
-      <c r="C11" s="64" t="s">
+      <c r="B11" s="58"/>
+      <c r="C11" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="65" t="s">
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="159"/>
+      <c r="I11" s="159"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="O11" s="65"/>
-      <c r="P11" s="65"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="65"/>
-      <c r="S11" s="63"/>
+      <c r="O11" s="161"/>
+      <c r="P11" s="161"/>
+      <c r="Q11" s="161"/>
+      <c r="R11" s="161"/>
+      <c r="S11" s="58"/>
     </row>
     <row r="12" spans="2:20" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B12" s="63"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="69"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="162"/>
+      <c r="O12" s="162"/>
+      <c r="P12" s="162"/>
+      <c r="Q12" s="162"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="59"/>
+      <c r="T12" s="60"/>
     </row>
     <row r="13" spans="2:20" ht="15.75">
-      <c r="B13" s="63"/>
-      <c r="C13" s="70" t="s">
+      <c r="B13" s="58"/>
+      <c r="C13" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="71" t="s">
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="O13" s="71" t="s">
+      <c r="O13" s="163" t="s">
         <v>70</v>
       </c>
-      <c r="P13" s="71" t="s">
+      <c r="P13" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="69"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="163"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="60"/>
     </row>
     <row r="14" spans="2:20" ht="15.75" customHeight="1">
-      <c r="B14" s="63"/>
-      <c r="C14" s="74" t="s">
+      <c r="B14" s="58"/>
+      <c r="C14" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="68"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="153"/>
+      <c r="H14" s="153"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="164"/>
+      <c r="O14" s="164"/>
+      <c r="P14" s="164"/>
+      <c r="Q14" s="164"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="59"/>
     </row>
     <row r="15" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B15" s="63"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="73" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="153"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="153"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="154" t="s">
         <v>72</v>
       </c>
-      <c r="O15" s="73" t="s">
+      <c r="O15" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="73" t="s">
+      <c r="P15" s="154" t="s">
         <v>97</v>
       </c>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="68"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="59"/>
     </row>
     <row r="16" spans="2:20" ht="15.75">
-      <c r="B16" s="63"/>
-      <c r="C16" s="74" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="68"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="155"/>
+      <c r="O16" s="155"/>
+      <c r="P16" s="155"/>
+      <c r="Q16" s="155"/>
+      <c r="R16" s="155"/>
+      <c r="S16" s="59"/>
     </row>
     <row r="17" spans="2:19" ht="15.75">
-      <c r="B17" s="63"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="63"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="73" t="s">
+      <c r="B17" s="58"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="O17" s="73" t="s">
+      <c r="O17" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="P17" s="76">
+      <c r="P17" s="156">
         <v>46174</v>
       </c>
-      <c r="Q17" s="76"/>
-      <c r="R17" s="76"/>
-      <c r="S17" s="68"/>
+      <c r="Q17" s="156"/>
+      <c r="R17" s="156"/>
+      <c r="S17" s="59"/>
     </row>
     <row r="18" spans="2:19" ht="15.75">
-      <c r="B18" s="63"/>
-      <c r="C18" s="74" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="77"/>
-      <c r="S18" s="68"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="153"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="155"/>
+      <c r="O18" s="155"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="157"/>
+      <c r="S18" s="59"/>
     </row>
     <row r="19" spans="2:19" ht="15.75">
-      <c r="B19" s="63"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="73" t="s">
+      <c r="B19" s="58"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="154" t="s">
         <v>73</v>
       </c>
-      <c r="O19" s="73" t="s">
+      <c r="O19" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="P19" s="78" t="s">
+      <c r="P19" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="68"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="59"/>
     </row>
     <row r="20" spans="2:19" ht="15.75">
-      <c r="B20" s="63"/>
-      <c r="C20" s="74" t="s">
+      <c r="B20" s="58"/>
+      <c r="C20" s="153" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="79" t="s">
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="155"/>
+      <c r="P20" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="68"/>
+      <c r="Q20" s="63"/>
+      <c r="R20" s="63"/>
+      <c r="S20" s="59"/>
     </row>
     <row r="21" spans="2:19" ht="15.75">
-      <c r="B21" s="63"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="73" t="s">
+      <c r="B21" s="58"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="153"/>
+      <c r="I21" s="153"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="154" t="s">
         <v>98</v>
       </c>
-      <c r="O21" s="73" t="s">
+      <c r="O21" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="P21" s="91" t="s">
+      <c r="P21" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="Q21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="68"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="59"/>
     </row>
     <row r="22" spans="2:19" ht="15.75">
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="75"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="92" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="155"/>
+      <c r="O22" s="155"/>
+      <c r="P22" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="92"/>
-      <c r="R22" s="92"/>
-      <c r="S22" s="68"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="59"/>
     </row>
     <row r="23" spans="2:19" ht="15.75">
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="68"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="59"/>
     </row>
     <row r="24" spans="2:19" ht="15.75">
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="68"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="59"/>
     </row>
     <row r="25" spans="2:19" ht="15.75">
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="63"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="63"/>
-      <c r="S25" s="68"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="59"/>
     </row>
     <row r="26" spans="2:19" ht="15.75">
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="68"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="152"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="59"/>
     </row>
     <row r="27" spans="2:19" ht="15.75">
-      <c r="B27" s="63"/>
-      <c r="C27" s="89" t="s">
+      <c r="B27" s="58"/>
+      <c r="C27" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="81" t="s">
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="152"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="68"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="65"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="59"/>
     </row>
     <row r="28" spans="2:19" ht="15.75">
-      <c r="B28" s="63"/>
-      <c r="C28" s="63" t="s">
+      <c r="B28" s="58"/>
+      <c r="C28" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="84" t="s">
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="85"/>
-      <c r="S28" s="68"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="59"/>
     </row>
     <row r="29" spans="2:19" ht="15.75">
-      <c r="B29" s="63"/>
-      <c r="C29" s="63" t="s">
+      <c r="B29" s="58"/>
+      <c r="C29" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="86" t="s">
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="O29" s="87"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="68"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="59"/>
     </row>
     <row r="30" spans="2:19" ht="15.75">
-      <c r="B30" s="63"/>
-      <c r="C30" s="63" t="s">
+      <c r="B30" s="58"/>
+      <c r="C30" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="63"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
       <c r="N30"/>
-      <c r="O30" s="63"/>
-      <c r="P30" s="63"/>
-      <c r="Q30" s="63"/>
-      <c r="R30" s="63"/>
-      <c r="S30" s="68"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="59"/>
     </row>
     <row r="31" spans="2:19" ht="15.75">
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="63"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="63"/>
-      <c r="S31" s="68"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="59"/>
     </row>
     <row r="32" spans="2:19" ht="15.75">
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="63"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="63"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="63"/>
-      <c r="S32" s="68"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="59"/>
     </row>
     <row r="33" spans="19:19" ht="15.75">
-      <c r="S33" s="69"/>
+      <c r="S33" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C3:O7"/>
+    <mergeCell ref="C11:I12"/>
+    <mergeCell ref="N11:R12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:R14"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:R16"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="C16:I17"/>
     <mergeCell ref="N17:N18"/>
@@ -2557,16 +2558,6 @@
     <mergeCell ref="C20:I21"/>
     <mergeCell ref="N21:N22"/>
     <mergeCell ref="O21:O22"/>
-    <mergeCell ref="C3:O7"/>
-    <mergeCell ref="C11:I12"/>
-    <mergeCell ref="N11:R12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:R14"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:R16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C16:I17" location="'Trading Comps'!A1" display="Trading Comps" xr:uid="{B00BD242-6AF5-4239-89CF-92455A0C2EFE}"/>
@@ -2574,25 +2565,32 @@
     <hyperlink ref="C20:I21" location="Appendix!A1" display="Appendix" xr:uid="{0A97CAF3-48AA-4031-9581-28A161189DFD}"/>
     <hyperlink ref="C14:I15" location="Inputs!A1" display="Inputs" xr:uid="{2E611527-B67B-4561-874F-C6E238954A6D}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.39370078740157483" right="0.48" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9F4AC6-416A-4303-B830-4A1F6AD3141C}">
-  <dimension ref="B2:L25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="9" width="24.28515625" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="10" width="24.28515625" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="26.25">
+    <row r="2" spans="2:13" ht="26.25">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -2601,12 +2599,13 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="H2" s="26"/>
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
-    </row>
-    <row r="3" spans="2:12" ht="26.25">
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="2:13" ht="26.25">
       <c r="B3" s="28" t="s">
         <v>53</v>
       </c>
@@ -2620,159 +2619,164 @@
       <c r="F3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="I3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="J3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="K3" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="L3" s="39" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:13">
       <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="95">
+      <c r="D5" s="78">
         <f>2055.2*(2349591262/10000000)</f>
         <v>482887.9961662399</v>
       </c>
-      <c r="E5" s="95">
+      <c r="E5" s="78">
         <v>0</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="78">
         <f>1104+374</f>
         <v>1478</v>
       </c>
-      <c r="G5" s="95">
+      <c r="G5" s="78"/>
+      <c r="H5" s="78">
         <v>269</v>
       </c>
-      <c r="H5" s="95">
+      <c r="I5" s="78">
         <f>(2583+665)*-1</f>
         <v>-3248</v>
       </c>
-      <c r="I5" s="95">
+      <c r="J5" s="78">
         <v>-4247</v>
       </c>
-      <c r="J5" s="95">
+      <c r="K5" s="78">
         <v>-112</v>
       </c>
-      <c r="K5" s="17">
-        <f>SUM(D5:J5)</f>
+      <c r="L5" s="17">
+        <f>SUM(D5:K5)</f>
         <v>477027.9961662399</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:13">
       <c r="B6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="95">
+      <c r="D6" s="78">
         <f>287.7*1252.95</f>
         <v>360473.71500000003</v>
       </c>
-      <c r="E6" s="95">
+      <c r="E6" s="78">
         <f>60+2126.22</f>
         <v>2186.2199999999998</v>
       </c>
-      <c r="F6" s="95">
+      <c r="F6" s="78">
         <f>140.86+71.98</f>
         <v>212.84000000000003</v>
       </c>
-      <c r="G6" s="95">
+      <c r="G6" s="78"/>
+      <c r="H6" s="78">
         <v>365.72</v>
       </c>
-      <c r="H6" s="95">
+      <c r="I6" s="78">
         <f>(643.46+2365.33)*-1</f>
         <v>-3008.79</v>
       </c>
-      <c r="I6" s="95">
+      <c r="J6" s="78">
         <v>-20750.64</v>
       </c>
-      <c r="J6" s="95">
+      <c r="K6" s="78">
         <v>-12089.55</v>
       </c>
-      <c r="K6" s="17">
-        <f>SUM(D6:J6)</f>
+      <c r="L6" s="17">
+        <f>SUM(D6:K6)</f>
         <v>327389.51500000001</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:13">
       <c r="B7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="95">
+      <c r="D7" s="78">
         <f>410.45*177.23</f>
         <v>72744.053499999995</v>
       </c>
-      <c r="E7" s="95">
+      <c r="E7" s="78">
         <f>15.96+1046.72</f>
         <v>1062.68</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="78">
         <f>181.18+43.46</f>
         <v>224.64000000000001</v>
       </c>
-      <c r="G7" s="95">
+      <c r="G7" s="78"/>
+      <c r="H7" s="78">
         <v>383.23</v>
       </c>
-      <c r="H7" s="95">
+      <c r="I7" s="78">
         <f>(199.37+362.7)*-1</f>
         <v>-562.06999999999994</v>
       </c>
-      <c r="I7" s="95">
+      <c r="J7" s="78">
         <v>-4595.47</v>
       </c>
-      <c r="J7" s="95">
+      <c r="K7" s="78">
         <v>-4331.16</v>
       </c>
-      <c r="K7" s="17">
-        <f>SUM(D7:J7)</f>
+      <c r="L7" s="17">
+        <f>SUM(D7:K7)</f>
         <v>64925.903499999971</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:13">
       <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="95">
+      <c r="D8" s="78">
         <f>1014.8*(989561780/10000000)</f>
         <v>100420.7294344</v>
       </c>
-      <c r="E8" s="95">
+      <c r="E8" s="78">
         <f>302.14+1818.17</f>
         <v>2120.31</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="78">
         <f>608.64+90.56</f>
         <v>699.2</v>
       </c>
-      <c r="G8" s="95">
+      <c r="G8" s="78"/>
+      <c r="H8" s="78">
         <v>1401.33</v>
       </c>
-      <c r="H8" s="95">
+      <c r="I8" s="78">
         <f>(3046.57+373.92)*-1</f>
         <v>-3420.4900000000002</v>
       </c>
-      <c r="I8" s="95">
+      <c r="J8" s="78">
         <v>-868.2</v>
       </c>
-      <c r="J8" s="95">
+      <c r="K8" s="78">
         <v>-285.7</v>
       </c>
-      <c r="K8" s="17">
-        <f>SUM(D8:J8)</f>
+      <c r="L8" s="17">
+        <f>SUM(D8:K8)</f>
         <v>100067.17943439999</v>
       </c>
-      <c r="L8" s="16"/>
-    </row>
-    <row r="10" spans="2:12" ht="26.25">
+      <c r="M8" s="16"/>
+    </row>
+    <row r="10" spans="2:13" ht="26.25">
       <c r="B10" s="26" t="s">
         <v>29</v>
       </c>
@@ -2781,12 +2785,13 @@
       <c r="E10" s="27"/>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="H10" s="26"/>
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
-    </row>
-    <row r="11" spans="2:12" ht="26.25">
+      <c r="L10" s="27"/>
+    </row>
+    <row r="11" spans="2:13" ht="26.25">
       <c r="B11" s="31" t="s">
         <v>53</v>
       </c>
@@ -2800,189 +2805,195 @@
       <c r="F11" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G11" s="32"/>
+      <c r="H11" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="I11" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="J11" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="J11" s="40" t="s">
+      <c r="K11" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="38" t="s">
+      <c r="L11" s="38" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:13">
       <c r="B13" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="96">
+      <c r="D13" s="79">
         <v>44888.7</v>
       </c>
-      <c r="E13" s="97">
+      <c r="E13" s="80">
         <v>1583.1</v>
       </c>
-      <c r="F13" s="97">
+      <c r="F13" s="80">
         <v>6992.3</v>
       </c>
-      <c r="G13" s="98">
+      <c r="G13" s="80"/>
+      <c r="H13" s="81">
         <f>SUM(D13:F13)</f>
         <v>53464.1</v>
       </c>
-      <c r="H13" s="97">
+      <c r="I13" s="80">
         <v>231546</v>
       </c>
-      <c r="I13" s="101" t="s">
+      <c r="J13" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="101" t="s">
+      <c r="K13" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="K13" s="101" t="s">
+      <c r="L13" s="84" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:13">
       <c r="B14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="99">
+      <c r="D14" s="82">
         <v>14062</v>
       </c>
-      <c r="E14" s="99">
+      <c r="E14" s="82">
         <v>410</v>
       </c>
-      <c r="F14" s="99">
+      <c r="F14" s="82">
         <v>1333</v>
       </c>
-      <c r="G14" s="98">
+      <c r="G14" s="82"/>
+      <c r="H14" s="81">
         <f>SUM(D14:F14)</f>
         <v>15805</v>
       </c>
-      <c r="H14" s="99">
+      <c r="I14" s="82">
         <v>64468</v>
       </c>
-      <c r="I14" s="25">
-        <f>G14/H14</f>
+      <c r="J14" s="25">
+        <f>H14/I14</f>
         <v>0.24516038965067941</v>
       </c>
-      <c r="J14" s="16">
-        <f>H14*(1+0.12)</f>
+      <c r="K14" s="16">
+        <f>I14*(1+0.12)</f>
         <v>72204.160000000003</v>
       </c>
-      <c r="K14" s="17">
-        <f>J14*I14</f>
+      <c r="L14" s="17">
+        <f>K14*J14</f>
         <v>17701.600000000002</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:13">
       <c r="B15" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="99">
+      <c r="D15" s="82">
         <f>28325.09-377.08</f>
         <v>27948.01</v>
       </c>
-      <c r="E15" s="99">
+      <c r="E15" s="82">
         <v>85.17</v>
       </c>
-      <c r="F15" s="99">
+      <c r="F15" s="82">
         <v>1710.53</v>
       </c>
-      <c r="G15" s="98">
+      <c r="G15" s="82"/>
+      <c r="H15" s="81">
         <f>SUM(D15:F15)</f>
         <v>29743.709999999995</v>
       </c>
-      <c r="H15" s="99">
+      <c r="I15" s="82">
         <v>89913.33</v>
       </c>
-      <c r="I15" s="25">
-        <f t="shared" ref="I15:I17" si="0">G15/H15</f>
+      <c r="J15" s="25">
+        <f t="shared" ref="J15:J17" si="0">H15/I15</f>
         <v>0.33080423114125562</v>
       </c>
-      <c r="J15" s="16">
-        <f>H15*(1+0.042)</f>
+      <c r="K15" s="16">
+        <f>I15*(1+0.042)</f>
         <v>93689.689859999999</v>
       </c>
-      <c r="K15" s="17">
-        <f t="shared" ref="K15:K17" si="1">J15*I15</f>
+      <c r="L15" s="17">
+        <f t="shared" ref="L15:L17" si="1">K15*J15</f>
         <v>30992.945819999994</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:13">
       <c r="B16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="99">
+      <c r="D16" s="82">
         <v>2437.2800000000002</v>
       </c>
-      <c r="E16" s="99">
+      <c r="E16" s="82">
         <v>145.4</v>
       </c>
-      <c r="F16" s="99">
+      <c r="F16" s="82">
         <v>468.93</v>
       </c>
-      <c r="G16" s="98">
+      <c r="G16" s="82"/>
+      <c r="H16" s="81">
         <f>SUM(D16:F16)</f>
         <v>3051.61</v>
       </c>
-      <c r="H16" s="99">
+      <c r="I16" s="82">
         <v>13192.57</v>
       </c>
-      <c r="I16" s="25">
+      <c r="J16" s="25">
         <f t="shared" si="0"/>
         <v>0.23131277681300916</v>
       </c>
-      <c r="J16" s="16">
-        <f>H16*(1+0.05)</f>
+      <c r="K16" s="16">
+        <f>I16*(1+0.05)</f>
         <v>13852.1985</v>
       </c>
-      <c r="K16" s="17">
+      <c r="L16" s="17">
         <f t="shared" si="1"/>
         <v>3204.1905000000002</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:13">
       <c r="B17" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="99">
+      <c r="D17" s="82">
         <v>2192.84</v>
       </c>
-      <c r="E17" s="99">
+      <c r="E17" s="82">
         <v>137.03</v>
       </c>
-      <c r="F17" s="99">
+      <c r="F17" s="82">
         <v>626.67999999999995</v>
       </c>
-      <c r="G17" s="98">
+      <c r="G17" s="82"/>
+      <c r="H17" s="81">
         <f>SUM(D17:F17)</f>
         <v>2956.55</v>
       </c>
-      <c r="H17" s="99">
+      <c r="I17" s="82">
         <v>20290.43</v>
       </c>
-      <c r="I17" s="25">
+      <c r="J17" s="25">
         <f t="shared" si="0"/>
         <v>0.14571154973058728</v>
       </c>
-      <c r="J17" s="16">
-        <f>H17*(1+0.123)</f>
+      <c r="K17" s="16">
+        <f>I17*(1+0.123)</f>
         <v>22786.152890000001</v>
       </c>
-      <c r="K17" s="17">
+      <c r="L17" s="17">
         <f t="shared" si="1"/>
         <v>3320.2056500000003</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
-      <c r="G18" s="17"/>
-    </row>
-    <row r="19" spans="2:12" ht="26.25">
+    <row r="18" spans="2:13">
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="2:13" ht="26.25">
       <c r="B19" s="26" t="s">
         <v>48</v>
       </c>
@@ -2991,12 +3002,13 @@
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
+      <c r="H19" s="26"/>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
       <c r="K19" s="27"/>
-    </row>
-    <row r="20" spans="2:12" ht="26.25">
+      <c r="L19" s="27"/>
+    </row>
+    <row r="20" spans="2:13" ht="26.25">
       <c r="B20" s="31" t="s">
         <v>53</v>
       </c>
@@ -3007,158 +3019,167 @@
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="37" t="s">
+      <c r="H20" s="35"/>
+      <c r="I20" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="37"/>
       <c r="J20" s="37"/>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="37"/>
+      <c r="L20" s="36" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:13">
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:13">
       <c r="B22" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="100">
+      <c r="D22" s="83">
         <v>10143</v>
       </c>
-      <c r="E22" s="100">
+      <c r="E22" s="83">
         <v>10282</v>
       </c>
-      <c r="F22" s="100">
+      <c r="F22" s="83">
         <v>10671</v>
       </c>
-      <c r="G22" s="100">
+      <c r="G22" s="83"/>
+      <c r="H22" s="83">
         <v>15059</v>
       </c>
-      <c r="H22" s="25">
+      <c r="I22" s="25">
         <f>(E22-D22)/E22</f>
         <v>1.3518770667185372E-2</v>
       </c>
-      <c r="I22" s="25">
-        <f t="shared" ref="I22:J22" si="2">(F22-E22)/F22</f>
+      <c r="J22" s="25">
+        <f>(F22-E22)/F22</f>
         <v>3.6453940586636681E-2</v>
       </c>
-      <c r="J22" s="25">
-        <f t="shared" si="2"/>
+      <c r="K22" s="25">
+        <f>(H22-F22)/H22</f>
         <v>0.29138721030612924</v>
       </c>
-      <c r="K22" s="25">
-        <f>AVERAGE(H22:J22)/3</f>
+      <c r="L22" s="25">
+        <f>AVERAGE(I22:K22)/3</f>
         <v>3.7928880173327927E-2</v>
       </c>
-      <c r="L22" s="24"/>
-    </row>
-    <row r="23" spans="2:12">
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="100">
+      <c r="D23" s="83">
         <v>19477</v>
       </c>
-      <c r="E23" s="100">
+      <c r="E23" s="83">
         <v>20751</v>
       </c>
-      <c r="F23" s="100">
+      <c r="F23" s="83">
         <v>35052</v>
       </c>
-      <c r="G23" s="100">
+      <c r="G23" s="83"/>
+      <c r="H23" s="83">
         <v>21018</v>
       </c>
-      <c r="H23" s="25">
-        <f t="shared" ref="H23:H25" si="3">(E23-D23)/E23</f>
+      <c r="I23" s="25">
+        <f t="shared" ref="I23:I25" si="2">(E23-D23)/E23</f>
         <v>6.1394631584020046E-2</v>
       </c>
-      <c r="I23" s="25">
-        <f t="shared" ref="I23:I25" si="4">(F23-E23)/F23</f>
+      <c r="J23" s="25">
+        <f t="shared" ref="J23:J25" si="3">(F23-E23)/F23</f>
         <v>0.40799383772680586</v>
       </c>
-      <c r="J23" s="25">
-        <f t="shared" ref="J23:J25" si="5">(G23-F23)/G23</f>
+      <c r="K23" s="25">
+        <f t="shared" ref="K23:K25" si="4">(H23-F23)/H23</f>
         <v>-0.66771338852412221</v>
       </c>
-      <c r="K23" s="25">
-        <f t="shared" ref="K23:K25" si="6">AVERAGE(H23:J23)/3</f>
+      <c r="L23" s="25">
+        <f t="shared" ref="L23:L25" si="5">AVERAGE(I23:K23)/3</f>
         <v>-2.2036102134810703E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:12">
+    <row r="24" spans="2:13">
       <c r="B24" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="100">
+      <c r="D24" s="83">
         <v>1701</v>
       </c>
-      <c r="E24" s="100">
+      <c r="E24" s="83">
         <v>1811</v>
       </c>
-      <c r="F24" s="100">
+      <c r="F24" s="83">
         <v>1740</v>
       </c>
-      <c r="G24" s="100">
+      <c r="G24" s="83"/>
+      <c r="H24" s="83">
         <v>1869</v>
       </c>
-      <c r="H24" s="25">
+      <c r="I24" s="25">
+        <f t="shared" si="2"/>
+        <v>6.0739922694643844E-2</v>
+      </c>
+      <c r="J24" s="25">
         <f t="shared" si="3"/>
-        <v>6.0739922694643844E-2</v>
-      </c>
-      <c r="I24" s="25">
+        <v>-4.0804597701149428E-2</v>
+      </c>
+      <c r="K24" s="25">
         <f t="shared" si="4"/>
-        <v>-4.0804597701149428E-2</v>
-      </c>
-      <c r="J24" s="25">
+        <v>6.9020866773675763E-2</v>
+      </c>
+      <c r="L24" s="25">
         <f t="shared" si="5"/>
-        <v>6.9020866773675763E-2</v>
-      </c>
-      <c r="K24" s="25">
-        <f t="shared" si="6"/>
         <v>9.8840213074633532E-3</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:13">
       <c r="B25" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="100">
+      <c r="D25" s="83">
         <v>1320</v>
       </c>
-      <c r="E25" s="100">
+      <c r="E25" s="83">
         <v>1215</v>
       </c>
-      <c r="F25" s="100">
+      <c r="F25" s="83">
         <v>1287</v>
       </c>
-      <c r="G25" s="100">
+      <c r="G25" s="83"/>
+      <c r="H25" s="83">
         <v>1547</v>
       </c>
-      <c r="H25" s="25">
+      <c r="I25" s="25">
+        <f t="shared" si="2"/>
+        <v>-8.6419753086419748E-2</v>
+      </c>
+      <c r="J25" s="25">
         <f t="shared" si="3"/>
-        <v>-8.6419753086419748E-2</v>
-      </c>
-      <c r="I25" s="25">
+        <v>5.5944055944055944E-2</v>
+      </c>
+      <c r="K25" s="25">
         <f t="shared" si="4"/>
-        <v>5.5944055944055944E-2</v>
-      </c>
-      <c r="J25" s="25">
+        <v>0.16806722689075632</v>
+      </c>
+      <c r="L25" s="25">
         <f t="shared" si="5"/>
-        <v>0.16806722689075632</v>
-      </c>
-      <c r="K25" s="25">
-        <f t="shared" si="6"/>
         <v>1.5287947749821389E-2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.39370078740157483" right="0.48" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6DC7DE-525F-4412-BA3F-FFBA64F70097}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3184,118 +3205,118 @@
       <c r="L2" s="27"/>
     </row>
     <row r="4" spans="2:12" ht="15.75">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="C4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="D4" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="105" t="s">
+      <c r="E4" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="113"/>
-      <c r="G4" s="114" t="s">
+      <c r="F4" s="94"/>
+      <c r="G4" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="113"/>
-      <c r="I4" s="114" t="s">
+      <c r="H4" s="94"/>
+      <c r="I4" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="106"/>
-      <c r="K4" s="114" t="s">
+      <c r="J4" s="87"/>
+      <c r="K4" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="107"/>
+      <c r="L4" s="88"/>
     </row>
     <row r="5" spans="2:12" ht="15.75">
-      <c r="B5" s="53"/>
-      <c r="C5" s="94" t="s">
+      <c r="B5" s="166"/>
+      <c r="C5" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="108">
+      <c r="E5" s="89">
         <v>2026</v>
       </c>
-      <c r="F5" s="112">
+      <c r="F5" s="93">
         <v>2027</v>
       </c>
-      <c r="G5" s="115">
+      <c r="G5" s="96">
         <v>2026</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="93">
         <v>2027</v>
       </c>
-      <c r="I5" s="115">
+      <c r="I5" s="96">
         <v>2026</v>
       </c>
-      <c r="J5" s="112">
+      <c r="J5" s="93">
         <v>2027</v>
       </c>
-      <c r="K5" s="115">
+      <c r="K5" s="96">
         <v>2026</v>
       </c>
-      <c r="L5" s="109">
+      <c r="L5" s="90">
         <v>2027</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="111"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="92"/>
     </row>
     <row r="7" spans="2:12" ht="15.75">
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="117">
-        <f>Inputs!K5</f>
+      <c r="C7" s="98">
+        <f>Inputs!L5</f>
         <v>477027.9961662399</v>
       </c>
-      <c r="D7" s="118">
+      <c r="D7" s="98">
         <f>Inputs!D5</f>
         <v>482887.9961662399</v>
       </c>
-      <c r="E7" s="119">
-        <f>Inputs!G14</f>
+      <c r="E7" s="99">
+        <f>Inputs!H14</f>
         <v>15805</v>
       </c>
-      <c r="F7" s="118">
-        <f>Inputs!K14</f>
+      <c r="F7" s="98">
+        <f>Inputs!L14</f>
         <v>17701.600000000002</v>
       </c>
-      <c r="G7" s="120">
+      <c r="G7" s="100">
         <v>15059</v>
       </c>
-      <c r="H7" s="118">
-        <f>G7*(1+Inputs!K22)</f>
+      <c r="H7" s="98">
+        <f>G7*(1+Inputs!L22)</f>
         <v>15630.171006530145</v>
       </c>
-      <c r="I7" s="124">
+      <c r="I7" s="104">
         <f>C7/E7</f>
         <v>30.182094031397654</v>
       </c>
-      <c r="J7" s="125">
+      <c r="J7" s="105">
         <f>C7/F7</f>
         <v>26.948298242319328</v>
       </c>
-      <c r="K7" s="124">
+      <c r="K7" s="104">
         <f>D7/G7</f>
         <v>32.06640521722823</v>
       </c>
-      <c r="L7" s="126">
+      <c r="L7" s="106">
         <f>D7/H7</f>
         <v>30.894607356790505</v>
       </c>
@@ -3304,42 +3325,42 @@
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="117">
-        <f>Inputs!K6</f>
+      <c r="C8" s="98">
+        <f>Inputs!L6</f>
         <v>327389.51500000001</v>
       </c>
-      <c r="D8" s="118">
+      <c r="D8" s="98">
         <f>Inputs!D6</f>
         <v>360473.71500000003</v>
       </c>
-      <c r="E8" s="119">
-        <f>Inputs!G15</f>
+      <c r="E8" s="99">
+        <f>Inputs!H15</f>
         <v>29743.709999999995</v>
       </c>
-      <c r="F8" s="118">
-        <f>Inputs!K15</f>
+      <c r="F8" s="98">
+        <f>Inputs!L15</f>
         <v>30992.945819999994</v>
       </c>
-      <c r="G8" s="120">
+      <c r="G8" s="100">
         <v>21018.15</v>
       </c>
-      <c r="H8" s="118">
-        <f>G8*(1+Inputs!K23)</f>
+      <c r="H8" s="98">
+        <f>G8*(1+Inputs!L23)</f>
         <v>20554.991899915232</v>
       </c>
-      <c r="I8" s="124">
+      <c r="I8" s="104">
         <f t="shared" ref="I8:I10" si="0">C8/E8</f>
         <v>11.007016777664926</v>
       </c>
-      <c r="J8" s="125">
+      <c r="J8" s="105">
         <f t="shared" ref="J8:J10" si="1">C8/F8</f>
         <v>10.563355832691869</v>
       </c>
-      <c r="K8" s="124">
+      <c r="K8" s="104">
         <f t="shared" ref="K8:K10" si="2">D8/G8</f>
         <v>17.150591988352925</v>
       </c>
-      <c r="L8" s="126">
+      <c r="L8" s="106">
         <f t="shared" ref="L8:L10" si="3">D8/H8</f>
         <v>17.537039992775995</v>
       </c>
@@ -3348,86 +3369,86 @@
       <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="117">
-        <f>Inputs!K7</f>
+      <c r="C9" s="98">
+        <f>Inputs!L7</f>
         <v>64925.903499999971</v>
       </c>
-      <c r="D9" s="118">
+      <c r="D9" s="98">
         <f>Inputs!D7</f>
         <v>72744.053499999995</v>
       </c>
-      <c r="E9" s="119">
-        <f>Inputs!G16</f>
+      <c r="E9" s="99">
+        <f>Inputs!H16</f>
         <v>3051.61</v>
       </c>
-      <c r="F9" s="118">
-        <f>Inputs!K16</f>
+      <c r="F9" s="98">
+        <f>Inputs!L16</f>
         <v>3204.1905000000002</v>
       </c>
-      <c r="G9" s="120">
+      <c r="G9" s="100">
         <v>1868.69</v>
       </c>
-      <c r="H9" s="118">
-        <f>G9*(1+Inputs!K24)</f>
+      <c r="H9" s="98">
+        <f>G9*(1+Inputs!L24)</f>
         <v>1887.1601717770438</v>
       </c>
-      <c r="I9" s="124">
+      <c r="I9" s="104">
         <f t="shared" si="0"/>
         <v>21.275950563800738</v>
       </c>
-      <c r="J9" s="125">
+      <c r="J9" s="105">
         <f t="shared" si="1"/>
         <v>20.262810060762607</v>
       </c>
-      <c r="K9" s="124">
+      <c r="K9" s="104">
         <f t="shared" si="2"/>
         <v>38.92783366957601</v>
       </c>
-      <c r="L9" s="126">
+      <c r="L9" s="106">
         <f t="shared" si="3"/>
         <v>38.546835921987785</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75">
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="121">
-        <f>Inputs!K8</f>
+      <c r="C10" s="101">
+        <f>Inputs!L8</f>
         <v>100067.17943439999</v>
       </c>
-      <c r="D10" s="121">
+      <c r="D10" s="101">
         <f>Inputs!D8</f>
         <v>100420.7294344</v>
       </c>
-      <c r="E10" s="122">
-        <f>Inputs!G17</f>
+      <c r="E10" s="102">
+        <f>Inputs!H17</f>
         <v>2956.55</v>
       </c>
-      <c r="F10" s="121">
-        <f>Inputs!K17</f>
+      <c r="F10" s="101">
+        <f>Inputs!L17</f>
         <v>3320.2056500000003</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="103">
         <v>1546.8</v>
       </c>
-      <c r="H10" s="121">
-        <f>G10*(1+Inputs!K25)</f>
+      <c r="H10" s="101">
+        <f>G10*(1+Inputs!L25)</f>
         <v>1570.4473975794235</v>
       </c>
-      <c r="I10" s="127">
+      <c r="I10" s="107">
         <f t="shared" si="0"/>
         <v>33.845928340261452</v>
       </c>
-      <c r="J10" s="128">
+      <c r="J10" s="108">
         <f t="shared" si="1"/>
         <v>30.138849813233701</v>
       </c>
-      <c r="K10" s="127">
+      <c r="K10" s="107">
         <f t="shared" si="2"/>
         <v>64.921599065425397</v>
       </c>
-      <c r="L10" s="129">
+      <c r="L10" s="109">
         <f t="shared" si="3"/>
         <v>63.944026134960907</v>
       </c>
@@ -3477,36 +3498,36 @@
       <c r="B15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="130">
+      <c r="C15" s="110">
         <f>E15*I15</f>
         <v>1287295.0962803685</v>
       </c>
-      <c r="D15" s="144">
+      <c r="D15" s="111">
         <f>G15*K15</f>
         <v>1338979.2091912343</v>
       </c>
-      <c r="E15" s="147">
-        <f>Inputs!G13</f>
+      <c r="E15" s="126">
+        <f>Inputs!H13</f>
         <v>53464.1</v>
       </c>
-      <c r="F15" s="139"/>
-      <c r="G15" s="147">
+      <c r="F15" s="119"/>
+      <c r="G15" s="126">
         <v>34990.800000000003</v>
       </c>
-      <c r="H15" s="139"/>
-      <c r="I15" s="124">
+      <c r="H15" s="119"/>
+      <c r="I15" s="104">
         <f>AVERAGE(I7:I10)</f>
         <v>24.077747428281192</v>
       </c>
-      <c r="J15" s="125">
+      <c r="J15" s="105">
         <f>AVERAGE(J7:J10)</f>
         <v>21.978328487251876</v>
       </c>
-      <c r="K15" s="124">
+      <c r="K15" s="104">
         <f>AVERAGE(K7:K10)</f>
         <v>38.266607485145641</v>
       </c>
-      <c r="L15" s="136">
+      <c r="L15" s="116">
         <f>AVERAGE(L7:L10)</f>
         <v>37.730627351628797</v>
       </c>
@@ -3515,37 +3536,37 @@
       <c r="B16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="131">
+      <c r="C16" s="111">
         <f t="shared" ref="C16:C18" si="4">E16*I16</f>
         <v>1375579.021021073</v>
       </c>
-      <c r="D16" s="144">
+      <c r="D16" s="111">
         <f t="shared" ref="D16:D18" si="5">G16*K16</f>
         <v>1242072.6070201951</v>
       </c>
-      <c r="E16" s="148">
+      <c r="E16" s="127">
         <f>E15</f>
         <v>53464.1</v>
       </c>
-      <c r="F16" s="139"/>
-      <c r="G16" s="148">
+      <c r="F16" s="119"/>
+      <c r="G16" s="127">
         <f>G15</f>
         <v>34990.800000000003</v>
       </c>
-      <c r="H16" s="140"/>
-      <c r="I16" s="124">
+      <c r="H16" s="120"/>
+      <c r="I16" s="104">
         <f>MEDIAN(I7:I10)</f>
         <v>25.729022297599194</v>
       </c>
-      <c r="J16" s="125">
+      <c r="J16" s="105">
         <f>MEDIAN(J7:J10)</f>
         <v>23.605554151540968</v>
       </c>
-      <c r="K16" s="124">
+      <c r="K16" s="104">
         <f>MEDIAN(K7:K10)</f>
         <v>35.49711944340212</v>
       </c>
-      <c r="L16" s="136">
+      <c r="L16" s="116">
         <f>MEDIAN(L7:L10)</f>
         <v>34.720721639389147</v>
       </c>
@@ -3554,76 +3575,76 @@
       <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="131">
+      <c r="C17" s="111">
         <f t="shared" si="4"/>
         <v>1809542.0973765722</v>
       </c>
-      <c r="D17" s="144">
+      <c r="D17" s="111">
         <f t="shared" si="5"/>
         <v>2271658.6885784874</v>
       </c>
-      <c r="E17" s="148">
+      <c r="E17" s="127">
         <f t="shared" ref="E17:E18" si="6">E16</f>
         <v>53464.1</v>
       </c>
-      <c r="F17" s="142"/>
-      <c r="G17" s="148">
+      <c r="F17" s="122"/>
+      <c r="G17" s="127">
         <f t="shared" ref="G17:G18" si="7">G16</f>
         <v>34990.800000000003</v>
       </c>
-      <c r="H17" s="140"/>
-      <c r="I17" s="145">
+      <c r="H17" s="120"/>
+      <c r="I17" s="124">
         <f>MAX(I7:I10)</f>
         <v>33.845928340261452</v>
       </c>
-      <c r="J17" s="138">
+      <c r="J17" s="118">
         <f t="shared" ref="J17" si="8">MAX(J7:J10)</f>
         <v>30.138849813233701</v>
       </c>
-      <c r="K17" s="145">
+      <c r="K17" s="124">
         <f>MAX(K7:K10)</f>
         <v>64.921599065425397</v>
       </c>
-      <c r="L17" s="137">
+      <c r="L17" s="117">
         <f t="shared" ref="L17" si="9">MAX(L7:L10)</f>
         <v>63.944026134960907</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="15.75">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="133">
+      <c r="C18" s="113">
         <f t="shared" si="4"/>
         <v>588480.2457027554</v>
       </c>
-      <c r="D18" s="133">
+      <c r="D18" s="113">
         <f t="shared" si="5"/>
         <v>600112.93414605956</v>
       </c>
-      <c r="E18" s="149">
+      <c r="E18" s="128">
         <f t="shared" si="6"/>
         <v>53464.1</v>
       </c>
-      <c r="F18" s="143"/>
-      <c r="G18" s="149">
+      <c r="F18" s="123"/>
+      <c r="G18" s="128">
         <f t="shared" si="7"/>
         <v>34990.800000000003</v>
       </c>
-      <c r="H18" s="141"/>
-      <c r="I18" s="146">
+      <c r="H18" s="121"/>
+      <c r="I18" s="125">
         <f>MIN(I7:I10)</f>
         <v>11.007016777664926</v>
       </c>
-      <c r="J18" s="134">
+      <c r="J18" s="114">
         <f t="shared" ref="J18" si="10">MIN(J7:J10)</f>
         <v>10.563355832691869</v>
       </c>
-      <c r="K18" s="146">
+      <c r="K18" s="125">
         <f>MIN(K7:K10)</f>
         <v>17.150591988352925</v>
       </c>
-      <c r="L18" s="135">
+      <c r="L18" s="115">
         <f t="shared" ref="L18" si="11">MIN(L7:L10)</f>
         <v>17.537039992775995</v>
       </c>
@@ -3632,12 +3653,16 @@
   <mergeCells count="1">
     <mergeCell ref="B4:B5"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.39370078740157483" right="0.48" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CC6004-9AF6-47F2-B49D-F967F3E74FB2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3647,7 +3672,7 @@
     <col min="4" max="4" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5703125" customWidth="1"/>
     <col min="8" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3670,36 +3695,36 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="2:7">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="164" t="s">
+      <c r="E4" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="150" t="s">
+      <c r="F4" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="159" t="s">
+      <c r="G4" s="138" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
       <c r="E5" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="151">
+      <c r="F5" s="130">
         <v>2026</v>
       </c>
-      <c r="G5" s="160">
+      <c r="G5" s="139">
         <v>2026</v>
       </c>
     </row>
@@ -3707,9 +3732,9 @@
       <c r="B6" s="45"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="161"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="140"/>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="49">
@@ -3721,14 +3746,14 @@
       <c r="D7" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="166">
+      <c r="E7" s="144">
         <v>300</v>
       </c>
-      <c r="F7" s="153">
+      <c r="F7" s="132">
         <f>200/3*12</f>
         <v>800</v>
       </c>
-      <c r="G7" s="162">
+      <c r="G7" s="141">
         <f t="shared" ref="G7:G12" si="0">$E7/F7</f>
         <v>0.375</v>
       </c>
@@ -3743,13 +3768,13 @@
       <c r="D8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="166">
+      <c r="E8" s="144">
         <v>472.5</v>
       </c>
-      <c r="F8" s="153">
+      <c r="F8" s="132">
         <v>306</v>
       </c>
-      <c r="G8" s="162">
+      <c r="G8" s="141">
         <f t="shared" si="0"/>
         <v>1.5441176470588236</v>
       </c>
@@ -3764,14 +3789,14 @@
       <c r="D9" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="166">
+      <c r="E9" s="144">
         <v>1152</v>
       </c>
-      <c r="F9" s="153">
+      <c r="F9" s="132">
         <f>E9/4.5</f>
         <v>256</v>
       </c>
-      <c r="G9" s="162">
+      <c r="G9" s="141">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
@@ -3786,13 +3811,13 @@
       <c r="D10" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="166">
+      <c r="E10" s="144">
         <v>5100</v>
       </c>
-      <c r="F10" s="153">
+      <c r="F10" s="132">
         <v>705.5</v>
       </c>
-      <c r="G10" s="162">
+      <c r="G10" s="141">
         <f t="shared" si="0"/>
         <v>7.2289156626506026</v>
       </c>
@@ -3807,34 +3832,34 @@
       <c r="D11" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="166">
+      <c r="E11" s="144">
         <v>1900</v>
       </c>
-      <c r="F11" s="153">
+      <c r="F11" s="132">
         <v>324.39999999999998</v>
       </c>
-      <c r="G11" s="162">
+      <c r="G11" s="141">
         <f t="shared" si="0"/>
         <v>5.856966707768188</v>
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="154">
+      <c r="B12" s="133">
         <v>45781</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="156" t="s">
+      <c r="D12" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="157">
+      <c r="E12" s="136">
         <v>603</v>
       </c>
-      <c r="F12" s="158">
+      <c r="F12" s="137">
         <v>386</v>
       </c>
-      <c r="G12" s="163">
+      <c r="G12" s="142">
         <f t="shared" si="0"/>
         <v>1.5621761658031088</v>
       </c>
@@ -3879,15 +3904,15 @@
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
-      <c r="E17" s="167">
+      <c r="E17" s="145">
         <f>F17*G17</f>
         <v>813003.39608898631</v>
       </c>
-      <c r="F17" s="168">
-        <f>Inputs!H13</f>
+      <c r="F17" s="146">
+        <f>Inputs!I13</f>
         <v>231546</v>
       </c>
-      <c r="G17" s="137">
+      <c r="G17" s="117">
         <f>AVERAGE(G7:G12)</f>
         <v>3.5111960305467869</v>
       </c>
@@ -3898,15 +3923,15 @@
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="12"/>
-      <c r="E18" s="167">
+      <c r="E18" s="145">
         <f>F18*G18</f>
         <v>701836.32124352339</v>
       </c>
-      <c r="F18" s="168">
+      <c r="F18" s="146">
         <f>F17</f>
         <v>231546</v>
       </c>
-      <c r="G18" s="137">
+      <c r="G18" s="117">
         <f>MEDIAN(G7:G12)</f>
         <v>3.0310880829015545</v>
       </c>
@@ -3917,34 +3942,34 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="12"/>
-      <c r="E19" s="167">
+      <c r="E19" s="145">
         <f>F19*G19</f>
         <v>1673826.5060240964</v>
       </c>
-      <c r="F19" s="168">
+      <c r="F19" s="146">
         <f t="shared" ref="F19:F20" si="1">F18</f>
         <v>231546</v>
       </c>
-      <c r="G19" s="137">
+      <c r="G19" s="117">
         <f>MAX(G7:G12)</f>
         <v>7.2289156626506026</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="16.5">
-      <c r="B20" s="169" t="s">
+      <c r="B20" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="170"/>
-      <c r="D20" s="171"/>
-      <c r="E20" s="172">
+      <c r="C20" s="148"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="150">
         <f>F20*G20</f>
         <v>86829.75</v>
       </c>
-      <c r="F20" s="173">
+      <c r="F20" s="151">
         <f t="shared" si="1"/>
         <v>231546</v>
       </c>
-      <c r="G20" s="135">
+      <c r="G20" s="115">
         <f>MIN(G7:G12)</f>
         <v>0.375</v>
       </c>
@@ -3955,13 +3980,17 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.39370078740157483" right="0.48" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF827393-CBC2-4FB4-A6F5-991AB1B6D9C4}">
-  <dimension ref="B2:U13"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
@@ -3977,12 +4006,12 @@
       <c r="B2" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="2:6">
       <c r="B3">
@@ -4061,7 +4090,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.39370078740157483" right="0.48" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
